--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104652_W22.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104652_W22.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.2986</v>
+        <v>5.5278</v>
       </c>
       <c r="E2" t="n">
-        <v>5.2017</v>
+        <v>2.6501</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0969</v>
+        <v>2.8776</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.8225</v>
+        <v>-0.8157</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5453</v>
+        <v>-0.5511</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2771</v>
+        <v>-0.2646</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.8471</v>
+        <v>-0.8638</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.9218</v>
+        <v>-0.9383</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0247</v>
+        <v>0.0481</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3764</v>
+        <v>0.3871</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.3517</v>
+        <v>-0.3391</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="S2" t="n">
-        <v>3.8677</v>
+        <v>1.0962</v>
       </c>
       <c r="T2" t="n">
-        <v>3.7443</v>
+        <v>1.2259</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1234</v>
+        <v>-0.1297</v>
       </c>
       <c r="V2" t="n">
-        <v>3.4387</v>
+        <v>3.4262</v>
       </c>
       <c r="W2" t="n">
-        <v>3.4387</v>
+        <v>3.4262</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. NEEDHAM</t>
+          <t>S. MARTINEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.321</v>
+        <v>3.8295</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3997</v>
+        <v>0.0594</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9213</v>
+        <v>3.7701</v>
       </c>
       <c r="G3" t="n">
-        <v>3.5341</v>
+        <v>0.4463</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8441</v>
+        <v>0.6145</v>
       </c>
       <c r="I3" t="n">
-        <v>1.69</v>
+        <v>-0.1682</v>
       </c>
       <c r="J3" t="n">
-        <v>2.4995</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>1.42</v>
+        <v>-0.0452</v>
       </c>
       <c r="L3" t="n">
-        <v>1.0795</v>
+        <v>0.1259</v>
       </c>
       <c r="M3" t="n">
-        <v>1.0346</v>
+        <v>0.3655</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4241</v>
+        <v>0.6597</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6105</v>
+        <v>-0.2942</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9073</v>
+        <v>2.2763</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-1.3658</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0415</v>
+        <v>3.6421</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6793</v>
+        <v>0.0174</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0344</v>
+        <v>0.2549</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3551</v>
+        <v>-0.2375</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.7997</v>
+        <v>1.0895</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.7997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N. MARIC</t>
+          <t>D. NEEDHAM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.53</v>
+        <v>2.6338</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9949</v>
+        <v>1.5585</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5352</v>
+        <v>1.0753</v>
       </c>
       <c r="G4" t="n">
-        <v>2.2312</v>
+        <v>3.5362</v>
       </c>
       <c r="H4" t="n">
-        <v>2.6523</v>
+        <v>1.8439</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4211</v>
+        <v>1.6923</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9502</v>
+        <v>2.4856</v>
       </c>
       <c r="K4" t="n">
-        <v>2.7636</v>
+        <v>1.4134</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1866</v>
+        <v>1.0722</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7189</v>
+        <v>1.0506</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1113</v>
+        <v>0.4305</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6077</v>
+        <v>0.6201</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5878</v>
+        <v>2.0487</v>
       </c>
       <c r="S4" t="n">
-        <v>1.002</v>
+        <v>-0.021</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3357</v>
+        <v>0.2111</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6663</v>
+        <v>-0.232</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.1568</v>
+        <v>-1.792</v>
       </c>
       <c r="W4" t="n">
-        <v>-1.1568</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. MARTINEZ</t>
+          <t>O. LIVINGSTON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4354</v>
+        <v>2.4965</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.3231</v>
+        <v>0.6977</v>
       </c>
       <c r="F5" t="n">
-        <v>3.7585</v>
+        <v>1.7988</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4412</v>
+        <v>3.0621</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6118</v>
+        <v>0.3336</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1706</v>
+        <v>2.7286</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1096</v>
+        <v>3.1428</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.0315</v>
+        <v>0.4924</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1411</v>
+        <v>2.6504</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3316</v>
+        <v>-0.0806</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6433</v>
+        <v>-0.1588</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3117</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.361</v>
+        <v>-4.5526</v>
       </c>
       <c r="R5" t="n">
-        <v>3.6293</v>
+        <v>3.4145</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.3668</v>
+        <v>0.0278</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.1644</v>
+        <v>0.4733</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2024</v>
+        <v>-0.4455</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0927</v>
+        <v>0.5447</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0927</v>
+        <v>1.6342</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. FERRANDO</t>
+          <t>N. MARIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5135</v>
+        <v>2.3878</v>
       </c>
       <c r="E6" t="n">
-        <v>2.4106</v>
+        <v>0.921</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8971</v>
+        <v>1.4668</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.6495</v>
+        <v>2.2306</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1124</v>
+        <v>2.6428</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.7619</v>
+        <v>-0.4122</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1173</v>
+        <v>2.9301</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0346</v>
+        <v>2.7439</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.152</v>
+        <v>0.1862</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.5321</v>
+        <v>-0.6995</v>
       </c>
       <c r="N6" t="n">
-        <v>0.07779999999999999</v>
+        <v>-0.1011</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.6099</v>
+        <v>-0.5984</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2268</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9073</v>
+        <v>1.5934</v>
       </c>
       <c r="S6" t="n">
-        <v>0.522</v>
+        <v>0.8629</v>
       </c>
       <c r="T6" t="n">
-        <v>0.248</v>
+        <v>0.29</v>
       </c>
       <c r="U6" t="n">
-        <v>0.274</v>
+        <v>0.5729</v>
       </c>
       <c r="V6" t="n">
-        <v>1.9604</v>
+        <v>-1.1609</v>
       </c>
       <c r="W6" t="n">
-        <v>2.5068</v>
+        <v>-1.1609</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5463</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>O. LIVINGSTON</t>
+          <t>G. FERRANDO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4341</v>
+        <v>1.428</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0549</v>
+        <v>2.1793</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3792</v>
+        <v>-0.7513</v>
       </c>
       <c r="G7" t="n">
-        <v>3.0781</v>
+        <v>-1.6389</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3407</v>
+        <v>0.1202</v>
       </c>
       <c r="I7" t="n">
-        <v>2.7374</v>
+        <v>-1.7591</v>
       </c>
       <c r="J7" t="n">
-        <v>3.1915</v>
+        <v>-0.1221</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5155</v>
+        <v>0.0345</v>
       </c>
       <c r="L7" t="n">
-        <v>2.676</v>
+        <v>-0.1566</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1134</v>
+        <v>-1.5168</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1749</v>
+        <v>0.0857</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0614</v>
+        <v>-1.6025</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.1342</v>
+        <v>0.6829</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.5367</v>
+        <v>-0.2276</v>
       </c>
       <c r="R7" t="n">
-        <v>3.4025</v>
+        <v>0.9105</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0561</v>
+        <v>0.4343</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2389</v>
+        <v>0.0346</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8172</v>
+        <v>0.3997</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5463</v>
+        <v>1.9497</v>
       </c>
       <c r="W7" t="n">
-        <v>1.639</v>
+        <v>2.4945</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0927</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. BUSQUETS</t>
+          <t>M. SUSINSKAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0167</v>
+        <v>0.9782999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2884</v>
+        <v>1.1595</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3051</v>
+        <v>-0.1813</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6177</v>
+        <v>-2.347</v>
       </c>
       <c r="H8" t="n">
-        <v>1.7533</v>
+        <v>-0.3452</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.1355</v>
+        <v>-2.0018</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6593</v>
+        <v>-0.629</v>
       </c>
       <c r="K8" t="n">
-        <v>1.2672</v>
+        <v>0.0862</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6079</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0416</v>
+        <v>-1.718</v>
       </c>
       <c r="N8" t="n">
-        <v>0.486</v>
+        <v>-0.4314</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5276</v>
+        <v>-1.2866</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.4952</v>
+        <v>-0.2276</v>
       </c>
       <c r="R8" t="n">
-        <v>3.1757</v>
+        <v>0.9105</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8111</v>
+        <v>0.4634</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5474</v>
+        <v>-0.1628</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2637</v>
+        <v>0.6262</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0927</v>
+        <v>2.1789</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.1789</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. SUSINSKAS</t>
+          <t>P. BUSQUETS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7471</v>
+        <v>0.951</v>
       </c>
       <c r="E9" t="n">
-        <v>0.795</v>
+        <v>-1.024</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.048</v>
+        <v>1.975</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.3622</v>
+        <v>0.6142</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3551</v>
+        <v>1.7493</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.0071</v>
+        <v>-1.1351</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6251</v>
+        <v>0.6211</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0866</v>
+        <v>1.2476</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7117</v>
+        <v>-0.6264999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.7371</v>
+        <v>-0.0069</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4417</v>
+        <v>0.5018</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.2954</v>
+        <v>-0.5086000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2268</v>
+        <v>-2.5039</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9073</v>
+        <v>3.1868</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2435</v>
+        <v>0.7433</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5383</v>
+        <v>0.8589</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7818000000000001</v>
+        <v>-0.1155</v>
       </c>
       <c r="V9" t="n">
-        <v>2.1853</v>
+        <v>-1.0895</v>
       </c>
       <c r="W9" t="n">
-        <v>2.1853</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="10">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.4557</v>
+        <v>-3.8113</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.2672</v>
+        <v>-4.8005</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8115</v>
+        <v>0.9892</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.2818</v>
+        <v>-4.2886</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.2511</v>
+        <v>-1.2494</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.0308</v>
+        <v>-3.0392</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.4374</v>
+        <v>-3.4601</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.4861</v>
+        <v>-1.4931</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.9513</v>
+        <v>-1.967</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8444</v>
+        <v>-0.8285</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2351</v>
+        <v>0.2437</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.0795</v>
+        <v>-1.0722</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R10" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1739</v>
+        <v>0.4773</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4688</v>
+        <v>0.0253</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2949</v>
+        <v>0.452</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.236</v>
+        <v>-4.1002</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.7682</v>
+        <v>-5.7911</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5322</v>
+        <v>1.6908</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.9999</v>
+        <v>-4.0095</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6595</v>
+        <v>0.6578000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-4.6594</v>
+        <v>-4.6673</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.7528</v>
+        <v>-3.7838</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1416</v>
+        <v>0.1272</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.8945</v>
+        <v>-3.911</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2471</v>
+        <v>-0.2257</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5178</v>
+        <v>0.5306</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.7649</v>
+        <v>-0.7563</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.597</v>
+        <v>0.5435</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.747</v>
+        <v>0.2691</v>
       </c>
       <c r="U11" t="n">
-        <v>0.15</v>
+        <v>0.2744</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>11.6047</v>
+        <v>12.3212</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.7901</v>
+        <v>-2.390100000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>14.3948</v>
+        <v>14.711</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.2136</v>
+        <v>-3.2103</v>
       </c>
       <c r="H12" t="n">
-        <v>5.8226</v>
+        <v>5.8164</v>
       </c>
       <c r="I12" t="n">
-        <v>-9.036099999999999</v>
+        <v>-9.026599999999998</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6304000000000003</v>
+        <v>0.4014999999999982</v>
       </c>
       <c r="K12" t="n">
-        <v>3.7897</v>
+        <v>3.6686</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.1596</v>
+        <v>-3.2671</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.843700000000001</v>
+        <v>-3.6118</v>
       </c>
       <c r="N12" t="n">
-        <v>2.0326</v>
+        <v>2.1478</v>
       </c>
       <c r="O12" t="n">
-        <v>-5.876499999999999</v>
+        <v>-5.759599999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>6.805</v>
+        <v>6.829</v>
       </c>
       <c r="Q12" t="n">
-        <v>-15.8784</v>
+        <v>-15.9342</v>
       </c>
       <c r="R12" t="n">
-        <v>22.6832</v>
+        <v>22.7631</v>
       </c>
       <c r="S12" t="n">
-        <v>3.931800000000001</v>
+        <v>4.645099999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>2.7524</v>
+        <v>3.4803</v>
       </c>
       <c r="U12" t="n">
-        <v>1.1794</v>
+        <v>1.165</v>
       </c>
       <c r="V12" t="n">
-        <v>4.081499999999999</v>
+        <v>4.057099999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>9.7057</v>
+        <v>9.6624</v>
       </c>
       <c r="X12" t="n">
-        <v>-5.624099999999999</v>
+        <v>-5.6052</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.4286</v>
+        <v>3.9466</v>
       </c>
       <c r="E13" t="n">
-        <v>1.5929</v>
+        <v>2.2641</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8358</v>
+        <v>1.6825</v>
       </c>
       <c r="G13" t="n">
-        <v>2.2023</v>
+        <v>2.1905</v>
       </c>
       <c r="H13" t="n">
-        <v>1.5787</v>
+        <v>1.5741</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6237</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>1.9508</v>
+        <v>1.9148</v>
       </c>
       <c r="K13" t="n">
-        <v>2.0363</v>
+        <v>2.02</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.08550000000000001</v>
+        <v>-0.1051</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2515</v>
+        <v>0.2757</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4576</v>
+        <v>-0.4458</v>
       </c>
       <c r="O13" t="n">
-        <v>0.7091</v>
+        <v>0.7215</v>
       </c>
       <c r="P13" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2689</v>
+        <v>0.2521</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9043</v>
+        <v>-0.1955</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6354</v>
+        <v>0.4476</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W13" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="14">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.1644</v>
+        <v>2.9987</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0432</v>
+        <v>2.5997</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1212</v>
+        <v>0.399</v>
       </c>
       <c r="G14" t="n">
-        <v>1.9891</v>
+        <v>1.9868</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.6276</v>
+        <v>-2.6279</v>
       </c>
       <c r="I14" t="n">
-        <v>4.6167</v>
+        <v>4.6147</v>
       </c>
       <c r="J14" t="n">
-        <v>1.7852</v>
+        <v>1.7544</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.2796</v>
+        <v>-2.2967</v>
       </c>
       <c r="L14" t="n">
-        <v>4.0648</v>
+        <v>4.0511</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2038</v>
+        <v>0.2324</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.348</v>
+        <v>-0.3312</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5518999999999999</v>
+        <v>0.5636</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.0515</v>
+        <v>-1.2158</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8347</v>
+        <v>-0.2442</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.2168</v>
+        <v>-0.9716</v>
       </c>
       <c r="V14" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W14" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1579,58 +1579,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8487</v>
+        <v>0.603</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1018</v>
+        <v>-0.1022</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9505</v>
+        <v>0.7052</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1628</v>
+        <v>0.1663</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1891</v>
+        <v>-0.1868</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3519</v>
+        <v>0.3531</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1255</v>
+        <v>0.129</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1891</v>
+        <v>-0.1868</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3145</v>
+        <v>0.3159</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2323</v>
+        <v>-0.0185</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1391</v>
+        <v>-0.1394</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3714</v>
+        <v>0.1209</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. PUSTOVYI</t>
+          <t>C. ORTEGA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2676</v>
+        <v>0.1668</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.5737</v>
+        <v>-1.6747</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3061</v>
+        <v>1.8415</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1271</v>
+        <v>1.0332</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0809</v>
+        <v>0.4104</v>
       </c>
       <c r="I16" t="n">
-        <v>0.208</v>
+        <v>0.6227</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7682</v>
+        <v>1.1314</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5817</v>
+        <v>0.655</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1866</v>
+        <v>0.4764</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6411</v>
+        <v>-0.0982</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6626</v>
+        <v>-0.2446</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0214</v>
+        <v>0.1463</v>
       </c>
       <c r="P16" t="n">
-        <v>-3.1757</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q16" t="n">
-        <v>-4.5367</v>
+        <v>-2.2763</v>
       </c>
       <c r="R16" t="n">
-        <v>1.361</v>
+        <v>1.8211</v>
       </c>
       <c r="S16" t="n">
-        <v>1.6882</v>
+        <v>-0.4112</v>
       </c>
       <c r="T16" t="n">
-        <v>2.102</v>
+        <v>-0.5298</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4138</v>
+        <v>0.1187</v>
       </c>
       <c r="V16" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2793</v>
+        <v>-0.1014</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4625</v>
+        <v>-0.3494</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1831</v>
+        <v>0.248</v>
       </c>
       <c r="G17" t="n">
-        <v>1.1276</v>
+        <v>1.1296</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1414</v>
+        <v>0.1435</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9862</v>
+        <v>0.9861</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6717</v>
+        <v>0.6703</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6717</v>
+        <v>0.6703</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4559</v>
+        <v>0.4593</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1414</v>
+        <v>0.1435</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3145</v>
+        <v>0.3159</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2728</v>
+        <v>-0.0929</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>0.1184</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2728</v>
+        <v>-0.2113</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. ORTEGA</t>
+          <t>R. LUZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5432</v>
+        <v>-1.2293</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.8931</v>
+        <v>-1.3912</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3498</v>
+        <v>0.1619</v>
       </c>
       <c r="G18" t="n">
-        <v>1.0265</v>
+        <v>-0.6977</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4054</v>
+        <v>0.0946</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6211</v>
+        <v>-0.7923</v>
       </c>
       <c r="J18" t="n">
-        <v>1.1404</v>
+        <v>0.1164</v>
       </c>
       <c r="K18" t="n">
-        <v>0.658</v>
+        <v>0.3103</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4824</v>
+        <v>-0.1939</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.114</v>
+        <v>-0.8141</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2526</v>
+        <v>-0.2157</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1387</v>
+        <v>-0.5984</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.4537</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8147</v>
+        <v>0.6829</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.116</v>
+        <v>0.1301</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7652</v>
+        <v>-0.3207</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3508</v>
+        <v>0.4509</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.9317</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. LUZ</t>
+          <t>A. PUSTOVYI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4068</v>
+        <v>-1.7021</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6097</v>
+        <v>-2.1317</v>
       </c>
       <c r="F19" t="n">
-        <v>0.203</v>
+        <v>0.4296</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7060999999999999</v>
+        <v>0.1445</v>
       </c>
       <c r="H19" t="n">
-        <v>0.09080000000000001</v>
+        <v>-0.075</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.797</v>
+        <v>0.2195</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1224</v>
+        <v>0.7583</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3117</v>
+        <v>0.5721000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.1893</v>
+        <v>0.1862</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8285</v>
+        <v>-0.6138</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2209</v>
+        <v>-0.6471</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6077</v>
+        <v>0.0333</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.5878</v>
+        <v>-3.1868</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.2683</v>
+        <v>-4.5526</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6805</v>
+        <v>1.3658</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0448</v>
+        <v>0.2508</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5565</v>
+        <v>0.5732</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5117</v>
+        <v>-0.3224</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9320000000000001</v>
+        <v>1.0895</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>K. KOSTADINOV</t>
+          <t>J. MCKOY</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6558</v>
+        <v>-2.0072</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4727</v>
+        <v>-2.7069</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1831</v>
+        <v>0.6997</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0759</v>
+        <v>-4.174</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9609</v>
+        <v>-3.6617</v>
       </c>
       <c r="I20" t="n">
-        <v>0.885</v>
+        <v>-0.5123</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.151</v>
+        <v>-3.4601</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.8974</v>
+        <v>-3.0724</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7463</v>
+        <v>-0.3877</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0751</v>
+        <v>-0.7139</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0636</v>
+        <v>-0.5893</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1387</v>
+        <v>-0.1246</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.1342</v>
+        <v>1.5934</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1342</v>
+        <v>1.5934</v>
       </c>
       <c r="S20" t="n">
-        <v>1.354</v>
+        <v>-0.129</v>
       </c>
       <c r="T20" t="n">
-        <v>0.9467</v>
+        <v>0.0507</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4074</v>
+        <v>-0.1797</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.7997</v>
+        <v>0.7025</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.7025</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.7997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. RICE</t>
+          <t>Y. PONS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1689</v>
+        <v>-2.207</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.521</v>
+        <v>-0.209</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6479</v>
+        <v>-1.998</v>
       </c>
       <c r="G21" t="n">
-        <v>4.4651</v>
+        <v>2.2413</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7895</v>
+        <v>-0.8763</v>
       </c>
       <c r="I21" t="n">
-        <v>3.6756</v>
+        <v>3.1176</v>
       </c>
       <c r="J21" t="n">
-        <v>4.2185</v>
+        <v>1.2918</v>
       </c>
       <c r="K21" t="n">
-        <v>1.4679</v>
+        <v>-0.8898</v>
       </c>
       <c r="L21" t="n">
-        <v>2.7506</v>
+        <v>2.1816</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2466</v>
+        <v>0.9495</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6785</v>
+        <v>0.0135</v>
       </c>
       <c r="O21" t="n">
-        <v>0.925</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>-5.444</v>
+        <v>0.6829</v>
       </c>
       <c r="Q21" t="n">
-        <v>-7.9391</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>2.4952</v>
+        <v>1.8211</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6097</v>
+        <v>-0.7733</v>
       </c>
       <c r="T21" t="n">
-        <v>1.107</v>
+        <v>-0.3627</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4972</v>
+        <v>-0.4107</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.7997</v>
+        <v>-4.3579</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.8924</v>
+        <v>-4.3579</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. MCKOY</t>
+          <t>K. KOSTADINOV</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.5564</v>
+        <v>-2.6543</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.9179</v>
+        <v>-2.4342</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3615</v>
+        <v>-0.22</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.1723</v>
+        <v>-0.0737</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.6578</v>
+        <v>-0.9648</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.5144</v>
+        <v>0.8911</v>
       </c>
       <c r="J22" t="n">
-        <v>-3.4374</v>
+        <v>-0.1623</v>
       </c>
       <c r="K22" t="n">
-        <v>-3.0588</v>
+        <v>-0.907</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.3786</v>
+        <v>0.7447</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.7348</v>
+        <v>0.0886</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.599</v>
+        <v>-0.0578</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1359</v>
+        <v>0.1463</v>
       </c>
       <c r="P22" t="n">
-        <v>1.5878</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5878</v>
+        <v>1.1382</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.679</v>
+        <v>0.3496</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1875</v>
+        <v>0.0044</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4915</v>
+        <v>0.3452</v>
       </c>
       <c r="V22" t="n">
-        <v>0.7071</v>
+        <v>-1.792</v>
       </c>
       <c r="W22" t="n">
-        <v>0.7071</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Y. PONS</t>
+          <t>S. RICE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.1624</v>
+        <v>-3.0245</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.6526999999999999</v>
+        <v>-2.5457</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.5098</v>
+        <v>-0.4789</v>
       </c>
       <c r="G23" t="n">
-        <v>2.2396</v>
+        <v>4.4397</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.8817</v>
+        <v>0.7789</v>
       </c>
       <c r="I23" t="n">
-        <v>3.1213</v>
+        <v>3.6608</v>
       </c>
       <c r="J23" t="n">
-        <v>1.3162</v>
+        <v>4.1653</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.88</v>
+        <v>1.4404</v>
       </c>
       <c r="L23" t="n">
-        <v>2.1963</v>
+        <v>2.7249</v>
       </c>
       <c r="M23" t="n">
-        <v>0.9233</v>
+        <v>0.2745</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0017</v>
+        <v>-0.6615</v>
       </c>
       <c r="O23" t="n">
-        <v>0.925</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="P23" t="n">
-        <v>0.6805</v>
+        <v>-5.4632</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1342</v>
+        <v>-7.9671</v>
       </c>
       <c r="R23" t="n">
-        <v>1.8147</v>
+        <v>2.5039</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.7118</v>
+        <v>-0.2091</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8347</v>
+        <v>0.1667</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8771</v>
+        <v>-0.3758</v>
       </c>
       <c r="V23" t="n">
-        <v>-4.3707</v>
+        <v>-1.792</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X23" t="n">
-        <v>-4.3707</v>
+        <v>-2.8814</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.0061</v>
+        <v>-4.8341</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.8258</v>
+        <v>-6.0299</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8197</v>
+        <v>1.1958</v>
       </c>
       <c r="G24" t="n">
-        <v>-5.1721</v>
+        <v>-5.1761</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.4301</v>
+        <v>-0.4253</v>
       </c>
       <c r="I24" t="n">
-        <v>-4.742</v>
+        <v>-4.7508</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.5787</v>
+        <v>-4.6057</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0275</v>
+        <v>0.0205</v>
       </c>
       <c r="L24" t="n">
-        <v>-4.6062</v>
+        <v>-4.6261</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.5935</v>
+        <v>-0.5704</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.4576</v>
+        <v>-0.4458</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.1359</v>
+        <v>-0.1246</v>
       </c>
       <c r="P24" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R24" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.6713</v>
+        <v>-0.5018</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.113</v>
+        <v>-0.2861</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5583</v>
+        <v>-0.2157</v>
       </c>
       <c r="V24" t="n">
-        <v>0.6105</v>
+        <v>0.6162</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0.6105</v>
+        <v>0.6162</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-11.6048</v>
+        <v>-10.0448</v>
       </c>
       <c r="E25" t="n">
-        <v>-14.3948</v>
+        <v>-14.7111</v>
       </c>
       <c r="F25" t="n">
-        <v>2.789900000000001</v>
+        <v>4.6663</v>
       </c>
       <c r="G25" t="n">
-        <v>3.213699999999999</v>
+        <v>3.210399999999998</v>
       </c>
       <c r="H25" t="n">
-        <v>-5.822300000000001</v>
+        <v>-5.8163</v>
       </c>
       <c r="I25" t="n">
-        <v>9.036099999999998</v>
+        <v>9.026599999999998</v>
       </c>
       <c r="J25" t="n">
-        <v>3.843599999999999</v>
+        <v>3.6118</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.0327</v>
+        <v>-2.1476</v>
       </c>
       <c r="L25" t="n">
-        <v>5.876399999999998</v>
+        <v>5.7596</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.6302000000000001</v>
+        <v>-0.4014000000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>-3.7898</v>
+        <v>-3.668600000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>3.1593</v>
+        <v>3.2672</v>
       </c>
       <c r="P25" t="n">
-        <v>-6.8051</v>
+        <v>-6.829</v>
       </c>
       <c r="Q25" t="n">
-        <v>-22.6833</v>
+        <v>-22.7632</v>
       </c>
       <c r="R25" t="n">
-        <v>15.8785</v>
+        <v>15.9344</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.9319</v>
+        <v>-2.369</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.1793</v>
+        <v>-1.165</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.7524</v>
+        <v>-1.2039</v>
       </c>
       <c r="V25" t="n">
-        <v>-4.0814</v>
+        <v>-4.0572</v>
       </c>
       <c r="W25" t="n">
-        <v>5.624199999999999</v>
+        <v>5.6052</v>
       </c>
       <c r="X25" t="n">
-        <v>-9.7057</v>
+        <v>-9.662400000000002</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104652_W22.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104652_W22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104652_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104652_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104652_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104652_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104652_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104652_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104652_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104652_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104652_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104652_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-5.6052</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104652_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104652_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104652_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104652_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104652_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104652_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104652_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104652_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-4.3579</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104652_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104652_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-2.8814</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104652_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0.6162</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104652_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-9.662400000000002</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
